--- a/Source/Tesla/Documentation/2017 Updates/RB_updates_2017-03-22.xlsx
+++ b/Source/Tesla/Documentation/2017 Updates/RB_updates_2017-03-22.xlsx
@@ -262,7 +262,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -287,6 +287,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -300,7 +306,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -358,6 +364,21 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -936,26 +957,26 @@
       </c>
     </row>
     <row r="11" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A11" s="14">
+      <c r="A11" s="20">
         <v>10</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="B11" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="15" t="s">
+      <c r="C11" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15" t="s">
+      <c r="D11" s="21"/>
+      <c r="E11" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="F11" s="16" t="s">
+      <c r="F11" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="G11" s="17">
+      <c r="G11" s="23">
         <v>1</v>
       </c>
-      <c r="H11" s="18"/>
+      <c r="H11" s="24"/>
     </row>
     <row r="12" spans="1:8" ht="150" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
